--- a/user/common/csv/pageindex/DigiMPGSystemGuide/DigiMPGSystemGuide.xlsx
+++ b/user/common/csv/pageindex/DigiMPGSystemGuide/DigiMPGSystemGuide.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="pages" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="pages" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G37"/>
+  <dimension ref="A1:G38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -601,17 +601,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>マルチLLMサポート（GPT/Gemini/Claude/Grok）</t>
+          <t>マルチLLMサポート（GPT/Gemini/Claude/Grok/Llama/Azure OpenAI）</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>DigiM_FoundationModel.pyによる複数LLMプロバイダーの統一呼び出し。call_function_by_nameで関数名ベースのディスパッチ、エンジン設定のJSON定義</t>
+          <t>DigiM_FoundationModel.pyによる複数LLMプロバイダーの統一呼び出し。call_function_by_nameで関数名ベースのディスパッチ、エンジン設定のJSON定義。Azure OpenAI Service（generate_response_T_azure_openai）はAZURE_OPENAI_*環境変数とAPI versionの上書きに対応</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>インフラ,LLM,GPT,Gemini,Claude,Grok,エンジン</t>
+          <t>インフラ,LLM,GPT,Gemini,Claude,Grok,Llama,Azure OpenAI,エンジン,Foundation</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -643,12 +643,12 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>DALL-E/Geminiによる画像生成、画像MIMEタイプ自動判定、マルチモーダル入力（画像をLLMに渡す）の仕組み</t>
+          <t>DALL-E/gpt-image-1/Gemini/Azure DALL-E（generate_image_azure_dalle）による画像生成、画像MIMEタイプ自動判定、マルチモーダル入力（画像をLLMに渡す）の仕組み。output_format既定はpng</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>インフラ,画像生成,DALL-E,Gemini,マルチモーダル,MIME</t>
+          <t>インフラ,画像生成,DALL-E,gpt-image,Gemini,Azure,マルチモーダル,MIME</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -717,12 +717,12 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>テキストをEmbeddingモデルで数値ベクトル化、コサイン類似度による意味的近さの算出、バッチ埋め込み処理</t>
+          <t>テキストをEmbeddingモデルで数値ベクトル化、コサイン類似度による意味的近さの算出、バッチ埋め込み処理（250kトークン分割）。AZURE_OPENAI_EMBED_MODELでAzure経由Embeddingも可能</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>インフラ,ベクトル,Embedding,コサイン類似度,バッチ処理</t>
+          <t>インフラ,ベクトル,Embedding,Azure,コサイン類似度,バッチ処理</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -754,12 +754,12 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>ChromaDBのコレクション管理、メタデータ付きベクトル検索、whereフィルタ、シングルトンクライアントパターン</t>
+          <t>ChromaDBのコレクション管理、メタデータ付きベクトル検索（_build_where_limitationでSERVICE_ID/USER_ID/DEFINE_CODE条件を構築）、META_SEARCH BONUSによる日付ボーナス、Private Modeのwhereフィルタ、migrate_add_private_flagの一括マイグレーション、シングルトンクライアントパターン</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>インフラ,ChromaDB,ベクトルDB,コレクション,検索</t>
+          <t>インフラ,ChromaDB,ベクトルDB,コレクション,検索,META_SEARCH,Private</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
@@ -791,12 +791,12 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>ファイルベースのセッション保存（JSON/YAML/npy）、スレッドセーフなファイルロック、LOCK/UNLOCK/エラーのステータス管理とUI同期</t>
+          <t>ファイルベースのセッション保存（JSON/YAML/npy）、threading.Lockベースの_session_file_locks/_get_file_lockによるスレッドセーフなファイルロック、ZIPアーカイブ、LOCK/UNLOCK/エラーのステータス管理とUI同期</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>インフラ,セッション,永続化,ファイルロック,ステータス,スレッドセーフ</t>
+          <t>インフラ,セッション,永続化,ファイルロック,ステータス,スレッドセーフ,ZIP</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -828,12 +828,12 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>bcryptパスワードハッシュ、HMACクッキー認証。LOGIN_AUTH_METHODでJSON/RDB(PostgreSQL digim_users)を切替。Groupは配列でOR一致のエージェントフィルタ。Allowed設定で機能表示制御</t>
+          <t>bcryptパスワードハッシュ、HMAC-SHA256クッキー認証（COOKIE_SECRET、有効7日）。LOGIN_AUTH_METHODでJSON/RDB(PostgreSQL digim_users)を切替。Groupは配列でOR一致のエージェントフィルタ。Allowedで機能表示制御（Knowledge Explorer/User Memory Explorer/Scheduler/User Memory/User Memory Layers等）</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>インフラ,認証,セキュリティ,アクセス制御,グループ,bcrypt,RDB認証,JSONB,OR一致</t>
+          <t>インフラ,認証,セキュリティ,アクセス制御,bcrypt,HMAC,RDB認証,JSONB,Allowed</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -1013,12 +1013,12 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>古いセッションのZIP圧縮アーカイブ、PostgreSQLへのエクスポート（sessions/dialogs/references）、マスターデータ管理</t>
+          <t>古いセッションのZIP圧縮アーカイブ（既定30日、ARCHIVE_FOLDERはuser/archive/）、PostgreSQLへのエクスポート（digim_sessions/dialogs/references）、pgvector経由でAzure OpenAI Embeddingによる対話ベクトル化、マスターデータ管理</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>データ,アーカイブ,PostgreSQL,エクスポート,マスターデータ</t>
+          <t>データ,アーカイブ,PostgreSQL,pgvector,Azure OpenAI,エクスポート</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1272,12 +1272,12 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>アップロードファイル（テキスト/PDF/JSON/画像/音声/Office）の解析とプロンプト注入。Perplexity/OpenAI/GoogleによるWeb検索結果の付加。チャット入力中のhttp(s)リンク自動取得（DigiM_UrlFetch）でサブページクロールも可能</t>
+          <t>アップロードファイル（テキスト/PDF/JSON/画像/音声/Office）の解析とプロンプト注入。OpenAI/Perplexity/GoogleによるWeb検索結果の付加（WEB_SEARCH_DEFAULT既定OpenAI）。チャット入力中のhttp(s)リンク自動取得（DigiM_UrlFetch）でサブページクロール（URL_FETCH設定でtimeout/MAX_BYTES/許可・拒否ドメイン/blocklist/拒否拡張子を制御）</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>コンテキスト,コンテンツ,Web検索,URL取得,アップロード,PDF,画像,Office</t>
+          <t>コンテキスト,コンテンツ,Web検索,URL取得,UrlFetch,SSRF,Office</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
@@ -1383,12 +1383,12 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>セッション横断でユーザー理解を蓄積する3層メモリ。History(session_digest)/Nowaday(period_profile)/Persona(persona_profile)を Excel/Notion/RDB から層ごとに保存先選択。Knowledge直前にプロンプトコンテキストとして注入(# 対話相手について / ## 人物像 / ## 最近の傾向 / ## 直近セッション)。Historyはaxis_tags×時間ハイブリッド検索(MeCabで入力名詞抽出、タグは意味単位で保持)。PersonaはApproved/Pending/Deletedの3ステータス、confidence&gt;=USER_MEMORY_AUTO_APPROVE_THRESHOLDで自動承認、各フィールドUSER_MEMORY_PERSONA_MAX_CHARS_PER_FIELD字で打ち切り、approvedのみ注入。History生成はFeedback(role=feedback)も加味、SETTING.FLG=N/MEMORY_FLG=Nのseqは除外。Allowed['User Memory']で表示権限、Allowed['User Memory Layers']で有効層を制御。WebUIメイン画面BOOK直下のexpander(即時反映+Save+Review)、RAG Management&gt;User Memoryで管理者用統合更新ボタン(History→Nowaday→Persona、Period date、Target User IDs multiselect)。USER_MEMORY_NOWADAY_SCHEDULEで月次cron可。注入実績はresponse.reference.user_memory + prompt.user_memory_contextに記録、Detail Informationで確認</t>
+          <t>セッション横断でユーザー理解を蓄積する3層メモリ。History(session_digest)/Nowaday(period_profile)/Persona(persona_profile)を Excel/Notion/RDB から層ごとに保存先選択。Knowledge直前にプロンプトコンテキストとして注入(# 対話相手について / ## 人物像 / ## 最近の傾向 / ## 直近セッション)。Historyはaxis_tags×時間ハイブリッド検索(半減期USER_MEMORY_HISTORY_RECENCY_HALF_LIFE_DAYS)。プルチック8基本感情+二次感情(ダイアド)とBig5(score/confidence/status)を保持。PersonaはApproved/Pending/Deletedの3ステータス、confidence&gt;=AUTO_APPROVE_THRESHOLDで自動承認、各フィールドUSER_MEMORY_PERSONA_MAX_CHARS_PER_FIELD字で打ち切り、approvedのみ注入。IMAGEGENステップは自動スキップ。Nowaday更新はDigiM_Scheduler経由のcronで自動化可。注入実績はresponse.reference.user_memory + prompt.user_memory_contextに記録</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>コンテキスト,ユーザーメモリ,階層メモリ,History,Nowaday,Persona,axis_tags,MeCab,タグ検索,自動承認,User Memory Layers,Allowed,GraphRAG</t>
+          <t>コンテキスト,ユーザーメモリ,階層メモリ,History,Nowaday,Persona,プルチック,Big5,axis_tags,自動承認,Allowed</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
@@ -1457,12 +1457,12 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>トークン単位のリアルタイムストリーミング。バックグラウンドスレッド実行と2秒ポーリング。セッションロック制御と中間ダイジェストの誤UNLOCK防止。DigiM_JobRegistryでスレッド追跡・サイドバーから選択キャンセル。マルチペルソナ並列実行（DigiMatsuExecute_MultiPersona）で同seq内に各ペルソナの応答をsub_seq別に保存、自動MEMORY_FLG=N、Include Queryで次ターン入力に埋め込み可能。Practice内のchain.PERSONAS（Phase 6/7）にも対応、PersonaSelectorによる自動選定（agent_54PersonaSelector）と統合用agent_50PersonaMergeも提供。マジックワードのサンプル: 皆の意見を聞いて／適任に聞いて</t>
+          <t>トークン単位のリアルタイムストリーミング。バックグラウンドスレッド実行と2秒ポーリング。セッションロック制御と中間ダイジェストの誤UNLOCK防止。DigiM_JobRegistryでスレッド追跡・サイドバーから選択キャンセル。cron駆動の定期ジョブはDigiM_Scheduler（4-7）で別系統管理。マルチペルソナ並列実行（DigiMatsuExecute_MultiPersona）で同seq内に各ペルソナの応答をsub_seq別に保存。chain.PERSONAS（Phase 6/7）にも対応</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>アプリ,ストリーミング,バックグラウンド,非同期,ロック制御,JobRegistry,キャンセル,マルチペルソナ,Include Query,chain.PERSONAS,PersonaSelector</t>
+          <t>アプリ,ストリーミング,バックグラウンド,非同期,JobRegistry,Scheduler,キャンセル,マルチペルソナ</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
@@ -1531,12 +1531,12 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>RAGクエリ生成（深層心理推定）、日付抽出、会話ダイジェスト、セッション名生成、PageIndex検索、PersonaSelector（Phase 7: 質問内容に応じたペルソナ自動選定）、PersonaMerge（Phase 6: ペルソナ応答の統合・要約強度制御）。SUPPORT_AGENTで定義、ThreadPoolExecutorで並列実行</t>
+          <t>RAGクエリ生成(56)、日付抽出(55)、会話ダイジェスト(51)、セッション名生成(57)、PageIndex検索(59PageIndex)、Thinking(59Thinking)、PersonaSelector(54: 質問内容に応じたペルソナ自動選定)、PersonaMerge(50: 応答の統合・要約強度制御)、ArtCritic(52)、CompareTexts(53)、EthicalCheck(21)、SenryuSensei(22)、DataAnalyst(23)、UserMemoryHistory/Nowaday/Persona生成(58/59Nowaday/60Persona)。SUPPORT_AGENTで定義、ThreadPoolExecutorで並列実行</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>アプリ,サポートエージェント,RAGクエリ,日付抽出,ダイジェスト,PageIndexSearch,PersonaSelector,PersonaMerge</t>
+          <t>アプリ,サポートエージェント,RAGクエリ,日付抽出,ダイジェスト,PersonaSelector,UserMemory生成,Thinking</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
@@ -1600,17 +1600,17 @@
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>知識活用分析とエージェント比較</t>
+          <t>Knowledge Explorer（知識活用分析・PageIndex対応）</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>RAGチャンクの貢献度分析（質問類似度vs回答類似度の差分）、PCA/t-SNE可視化、エージェント比較、サポートエージェントベンチマーク、エシカルチェック</t>
+          <t>旧RAG ExplorerのKnowledge Explorer。サイドバーから切替アクセス。Overall(分布概観)/Trend(時系列・Focus Period)/Topic(クラスタリング)/Ask Agent(自然言語問い合わせ・agent_23DataAnalyst)/Generate Reportの5タブ。VectorDB(Collection)とPageIndexの両方に対応。エージェント比較・サポートエージェントベンチマーク・エシカルチェック・知識貢献度(質問類似度vs回答類似度差分)もここから実行。保存セッションで再現可。Allowed["Knowledge Explorer"]で権限制御</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>アプリ,分析,知識活用,PCA,t-SNE,比較,エシカル</t>
+          <t>アプリ,Knowledge Explorer,分析,Trend,Topic,Ask Agent,Generate Report,PageIndex,DataAnalyst</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
@@ -1642,12 +1642,12 @@
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>Streamlitベースのチャットインターフェース。エンジン選択、Book選択（BOOKが空でない時のみ表示）、Web検索トグル、Personas multiselect（ORG定義エージェントのみ）、Include Query（直前seqがマルチペルソナ時のみ表示）、Private/Thinking Modeトグル、Thinking Targets（PersonasはORGエージェントのみ）、Max Personas（Thinking Targetsに Personas 選択時のみ表示）、ファイルアップロード、Exec Setting。会話履歴のDelete（表示・参照とも除外）とMemory Off（表示は残しメモリ参照のみ除外）のseq単位制御。前提を満たさないコントロールは描画しない方針（Hide irrelevant sidebar controls）</t>
+          <t>Streamlitベースのチャットインターフェース。サイドバー上部のラジオ(Chat / Knowledge Explorer / User Memory Explorer / Scheduler)でメイン画面切替。エンジン選択、Book選択、Web検索トグル(WEB_SEARCH_DEFAULT既定OpenAI)、Personas multiselect(ORG定義エージェントのみ)、Include Query、Private/Thinking Modeトグル、Thinking Targets(Personas含む)、Max Personas、ファイルアップロード、Exec Setting。会話履歴のDelete(表示・参照とも除外)とMemory Off(表示は残しメモリ参照のみ除外)のseq単位制御。User Memory expanderで層On/Off</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>UI,チャット,Streamlit,エンジン選択,Book,Web検索,Memory Off,Personas,Include Query,Thinking Targets,Max Personas,条件付きUI</t>
+          <t>UI,チャット,Streamlit,Knowledge Explorer,User Memory Explorer,Scheduler,Memory Off,Personas</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
@@ -1753,12 +1753,12 @@
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>FastAPIエンドポイント: /run（メッセージ送信）、/sessions（履歴取得）、/agents（エージェント情報）、/feedback（フィードバック送信）。LINE/Slack連携対応</t>
+          <t>FastAPIエンドポイント: /run(エージェント実行、user_memory/user_memory_layersでメモリ注入制御)、/run_function(ツール関数直接呼出)、/sessions /sessions/{id}(履歴)、/agents /agents/{file}/engines /agents/{file}/feedback(エージェント情報)、/feedback(送信)、/web_search_engines、/health。LINE/Slack連携対応</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>UI,API,REST,FastAPI,LINE,Slack,外部連携</t>
+          <t>UI,API,REST,FastAPI,user_memory,run_function,health,LINE,Slack</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
@@ -1790,12 +1790,12 @@
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>ユーザーメモリ(Persona/Nowaday/History)を3タブで扱う。左から「マイメモリ」(自分のメモリ確認・修正)/「ユーザー理解(個人)」(深掘り+対話)/「グループ理解」(コホート横断+対話)。Big5・プルチック感情・関心トピック変遷の可視化とメモリ接地エージェント対話。DigiM_UserMemoryExplorer.py</t>
+          <t>ユーザーメモリ(Persona/Nowaday/History)を3タブで扱う。マイメモリ(自分のメモリ確認・編集)/ユーザー理解(個人)(深掘り+User Twin対話)/グループ理解(コホート横断+Group Twin対話)。Big5レーダー・プルチック感情トラジェクトリ・関心トピック変遷・PCA+K-Meansクラスタリング・ワードクラウドを可視化、Generate Reportで保存セッション再現可。バックエンドはDigiM_UserMemoryExplorer.py。Allowed["User Memory Explorer"]で権限制御(既定false)</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>UI,User Memory Explorer,マイメモリ,ユーザー理解,グループ理解,感情分析,Big5,対話</t>
+          <t>UI,User Memory Explorer,マイメモリ,User Twin,Group Twin,Big5,プルチック,クラスタリング</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
@@ -1806,6 +1806,43 @@
       <c r="G37" s="2" t="inlineStr">
         <is>
           <t>5-5.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr">
+        <is>
+          <t>DigiMPGシステムガイド</t>
+        </is>
+      </c>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
+          <t>4-7</t>
+        </is>
+      </c>
+      <c r="C38" s="2" t="inlineStr">
+        <is>
+          <t>スケジューラ（cron駆動の汎用ジョブ）</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
+        <is>
+          <t>DigiM_Scheduler + DigiM_ScheduledJobsによるcron駆動の汎用ジョブ実行基盤。kindは rag_update / user_memory_nowaday / agent_run の3種類。WebUI上部のSchedulerメニューから Add/Edit/Run Now/Enable/Disable/Delete/Reload Schedulers を操作。cron式またはmonthly/weekly等のプリセット。定義は user/common/mst/scheduled_jobs.json に永続化。Streamlit再起動なしでReload Schedulersで反映。Allowed["Scheduler"]で権限制御</t>
+        </is>
+      </c>
+      <c r="E38" s="2" t="inlineStr">
+        <is>
+          <t>アプリ,Scheduler,cron,JobRegistry,rag_update,user_memory_nowaday,agent_run,scheduled_jobs</t>
+        </is>
+      </c>
+      <c r="F38" s="2" t="inlineStr">
+        <is>
+          <t>アプリ層</t>
+        </is>
+      </c>
+      <c r="G38" s="2" t="inlineStr">
+        <is>
+          <t>4-7.md</t>
         </is>
       </c>
     </row>

--- a/user/common/csv/pageindex/DigiMPGSystemGuide/DigiMPGSystemGuide.xlsx
+++ b/user/common/csv/pageindex/DigiMPGSystemGuide/DigiMPGSystemGuide.xlsx
@@ -556,7 +556,7 @@
     <t>1. **Evaluation プラグイン**ドロップダウン 2. **Download template (.xlsx)** ボタン — プラグインの `sample_path()` が存在ファイルを指せばテンプレートをそのまま配信 3. **Upload input (.xlsx)** — 記入済 xlsx をアップロード 4. **Run analysis** ボタン → プラグイン解析実行 → render() 表示 5. **LLM Evaluation** — エ</t>
   </si>
   <si>
-    <t>人格評価7理論 (Big Five / Schwartz Value Theory / Self-Determination / Personal Strivings / Narrative Identity / Social Identity / Attachment) を一括スコアリング。`test/PersonalTestQA.xlsx` をテンプレートとして配布。</t>
+    <t xml:space="preserve">人格評価7理論 (Big Five / Schwartz Value Theory / Self-Determination / Personal Strivings / Narrative Identity / Social Identity / Attachment) を一括スコアリング。テンプレートはプラグインフォルダ直下に同梱 (`user/common/evaluation/PersonalEvaluation/PersonalTestQA.xlsx`) — UI </t>
   </si>
   <si>
     <t>`user/common/evaluation/&lt;新規名&gt;/main.py` に `Plugin` クラスを実装するだけで、サイドバーの Evaluation メニューに自動的にプラグインが現れます (再起動不要)。</t>

--- a/user/common/csv/pageindex/DigiMPGSystemGuide/DigiMPGSystemGuide.xlsx
+++ b/user/common/csv/pageindex/DigiMPGSystemGuide/DigiMPGSystemGuide.xlsx
@@ -438,7 +438,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G65"/>
+  <dimension ref="A1:G69"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -496,7 +496,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>本PGはApache2.0Licenceで公開しており、商用利用を認めています。 ただし、本PGを用いたユーザー側での活動に対して、開発者は一切の責任を負いませんので、あくまで御自身の責任においてPGを利用してください。</t>
+          <t>本PGはApache2.0Licenceで公開しており、商用利用を認めています。</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -531,6 +531,11 @@
           <t>本プログラム開発においてこだわっていること</t>
         </is>
       </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>- 作業効率化ではなく、人間の知識をAIが再現できるかが主目的</t>
+        </is>
+      </c>
       <c r="E3" t="inlineStr">
         <is>
           <t>本プログラム開発においてこだわっていること</t>
@@ -563,6 +568,11 @@
           <t>参考ドキュメント</t>
         </is>
       </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>- [概要とアーキテクチャの説明](docs/Overview_of_DigitalMATSUMOTO.pdf)</t>
+        </is>
+      </c>
       <c r="E4" t="inlineStr">
         <is>
           <t>DigitalMATSUMOTO,BF,ABMATSUMOTO,AE,BC,AD</t>
@@ -632,9 +642,14 @@
           <t>主要モジュール</t>
         </is>
       </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>| モジュール | 役割 |</t>
+        </is>
+      </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>DigiM_Execute,DigiM_Session,DigiM_Context,DigiM_FoundationModel,DigiM_Agent,DigiM_AgentPersona</t>
+          <t>DigiM_Execute,DigiM_Session,DigiM_Context,DigiM_FoundationModel,DigiM_Agent,DigiM_AgentPersona,DigiM_Execute.py,DigiM_Session.py</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -666,7 +681,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t xml:space="preserve">DigitalMATSUMOTO/ ├── user/ │   ├── common/ │   │   ├── agent/                # エージェント設定JSON │   │   ├── agent/persona_data/   # エージェントペルソナのxlsx（複数ペルソナ並列実行用） │   │   ├── practice/             # プラクティス設定JSON │   │   ├── tool/                </t>
+          <t>DigitalMATSUMOTO/</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -701,6 +716,7 @@
           <t>環境構築・インストレーション</t>
         </is>
       </c>
+      <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
           <t>環境構築・インストレーション</t>
@@ -733,6 +749,11 @@
           <t>前提条件</t>
         </is>
       </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>- Docker がインストール済みであること</t>
+        </is>
+      </c>
       <c r="E9" t="inlineStr">
         <is>
           <t>Docker,OpenAI,Google,Gemini,Anthropic,Claude</t>
@@ -767,7 +788,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>git clone https://github.com/m07takash/DigitalMATSUMOTO.git cd DigitalMATSUMOTO</t>
+          <t>git clone https://github.com/m07takash/DigitalMATSUMOTO.git</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -809,7 +830,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Docker,Python3,MeCab,IPAex,Noto,CJK</t>
+          <t>Docker,Python3,MeCab,IPAex,Noto,CJK,requirements.txt</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -846,7 +867,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>DigitalMATSUMOTO,Streamlit,WebUI,FastAPI</t>
+          <t>DigitalMATSUMOTO,Streamlit,WebUI,FastAPI,system.env</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -883,7 +904,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>OPENAI_API_KEY,OpenAI,GEMINI_API_KEY,ANTHROPIC_API_KEY,XAI_API_KEY,TIMEZONE</t>
+          <t>OPENAI_API_KEY,OpenAI,GEMINI_API_KEY,ANTHROPIC_API_KEY,XAI_API_KEY,TIMEZONE,system.env_sample,system.env</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -920,7 +941,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Streamlit,WebDigiMatsuAgent,WebUI,FastAPI</t>
+          <t>Streamlit,WebDigiMatsuAgent,WebUI,FastAPI,system.env,startup.sh_sample,startup.sh,.gitignore</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -994,7 +1015,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Nginx,VM,Let,Encrypt,PPTX,HTTP</t>
+          <t>Nginx,VM,Let,Encrypt,PPTX,HTTP,http,Upgrade</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -1061,6 +1082,7 @@
           <t>セットアップガイド</t>
         </is>
       </c>
+      <c r="D18" t="inlineStr"/>
       <c r="E18" t="inlineStr">
         <is>
           <t>セットアップガイド</t>
@@ -1100,7 +1122,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Notion,USER_MST_FILE,RAG_MST_FILE,PROMPT_TEMPLATE_MST_FILE,USER0001,Name</t>
+          <t>Notion,USER_MST_FILE,RAG_MST_FILE,PROMPT_TEMPLATE_MST_FILE,USER0001,Name,sample_,sample_users.json</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1137,7 +1159,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>RAG,Step,UTF,Sample01_Quote,Sample02_Memo,Sample03_Feedback</t>
+          <t>RAG,Step,UTF,Sample01_Quote,Sample02_Memo,Sample03_Feedback,Sample01_Quote.csv,Sample02_Memo.csv</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1174,7 +1196,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>PERSONALITY,SEX,BIRTHDAY,Jan,IS_ALIVE,NATIONALITY</t>
+          <t>PERSONALITY,SEX,BIRTHDAY,Jan,IS_ALIVE,NATIONALITY,agent_10Sample.json,SPEAKING_STYLE</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1211,7 +1233,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>NAME,Default,CHAIN,TYPE,LLM,AGENT_FILE</t>
+          <t>NAME,Default,CHAIN,TYPE,LLM,AGENT_FILE,IMAGEGEN,FUNC</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1248,7 +1270,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Web,WEB,Search,Perplexity,PERPLEXITY_API_KEY,OpenAI</t>
+          <t>Web,WEB,Search,Perplexity,PERPLEXITY_API_KEY,OpenAI,OPENAI_API_KEY,web_search_preview</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1285,7 +1307,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>SKILL,Tool,Slash,Command,LLM,GPT</t>
+          <t>SKILL,Tool,Slash,Command,LLM,GPT,DigiM_ToolRegistry.py,DigiM_Execute</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1322,7 +1344,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Citation,Injection,References,WebSearch,Web,URL</t>
+          <t>Citation,Injection,References,WebSearch,Web,URL,RAG_NAME,_parse_execution_settings</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1359,7 +1381,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>URL,DigiM_UrlFetch,Include,Subpages,OFF,MAX_BYTES</t>
+          <t>URL,DigiM_UrlFetch,Include,Subpages,OFF,MAX_BYTES,.exe,.dll</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1396,7 +1418,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>History,Nowaday,YYYY,MM,Persona,Big5</t>
+          <t>History,Nowaday,YYYY,MM,Persona,Big5,session_digest,period_profile</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1433,7 +1455,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>DigiM_JobRegistry,Sessions,Background,Jobs,PyThreadState_SetAsyncExc,SystemExit</t>
+          <t>DigiM_JobRegistry,Sessions,Background,Jobs,PyThreadState_SetAsyncExc,SystemExit,user_id,cancel_requested</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1507,7 +1529,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Knowledge,Explorer,Chat,Allowed,Overall,Trend</t>
+          <t>Knowledge,Explorer,Chat,Allowed,Overall,Trend,users.json</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1539,12 +1561,12 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>ラジオボタンで **Collection（VectorDB）** と **PageIndex** を切り替えます。コレクション一覧は、選択中のエージェントの KNOWLEDGE および BOOK 設定に基づいてフィルタリングされます。PageIndex 選択時はツリー構造表示・ページ感度分析の専用画面になります。</t>
+          <t>ラジオボタンで **Collection（VectorDB）** / **Graph** / **PageIndex** を切り替えます。コレクション一覧は、選択中のエージェントの KNOWLEDGE および BOOK 設定に基づいてフィルタリングされます。PageIndex 選択時はツリー構造表示・ページ感度分析の専用画面になります。</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Collection,VectorDB,PageIndex,KNOWLEDGE,BOOK,Persona</t>
+          <t>Collection,VectorDB,PageIndex,KNOWLEDGE,BOOK,Persona,st.data_editor,save_graph_atomic</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1618,7 +1640,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Trend,Total,NAME,View,Mode,RAG</t>
+          <t>Trend,Total,NAME,View,Mode,RAG,create_date</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1722,6 +1744,11 @@
           <t>PageIndex</t>
         </is>
       </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>- **ツリー構造表示**: ページインデックスの階層をツリー形式で可視化</t>
+        </is>
+      </c>
       <c r="E36" t="inlineStr">
         <is>
           <t>PageIndex</t>
@@ -1754,9 +1781,14 @@
           <t>エクスポート・レポート</t>
         </is>
       </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>**Generate Report** ボタンで分析セッションを保存し、グラフ埋め込みの `.md` ファイルをダウンロードできます。各セクションの解説は、**ドロップダウンで表示中のバージョン**がそのまま出力されます。</t>
+        </is>
+      </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Generate,Report</t>
+          <t>Generate,Report,.md</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1786,6 +1818,11 @@
           <t>セッション管理</t>
         </is>
       </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>| 項目 | 説明 |</t>
+        </is>
+      </c>
       <c r="E38" t="inlineStr">
         <is>
           <t>セッション管理</t>
@@ -1825,7 +1862,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>User,Memory,Explorer,Persona,Nowaday,History</t>
+          <t>User,Memory,Explorer,Persona,Nowaday,History,DigiM_UserMemoryExplorer.py,users.json</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1862,7 +1899,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Agent,Performance,Explorer,APE,User,Memory</t>
+          <t>Agent,Performance,Explorer,APE,User,Memory,DigiM_AgentPerformanceExplorer.py</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1894,12 +1931,12 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>session_id でユニオン de-dup (PG 優先)。これにより、すでに archive で圧縮済みのセッション・ライブのセッション・まだ Export していないセッション全部を横断集計できます。</t>
+          <t>| # | ソース | 用途 |</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>PG,PostgreSQL,Sessions,Export,DB,ZIP</t>
+          <t>PG,PostgreSQL,Sessions,Export,DB,ZIP,ARCHIVE_DAYS</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1929,6 +1966,11 @@
           <t>Tab 1: Overview</t>
         </is>
       </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>- メトリック: Sessions / Turns / Users / Total chars / Avg turns/session</t>
+        </is>
+      </c>
       <c r="E42" t="inlineStr">
         <is>
           <t>Tab,Overview,Sessions,Turns,Users,Total</t>
@@ -1968,7 +2010,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Tab,Knowledge,Book,Utilization,KNOWLEDGE,BOOK</t>
+          <t>Tab,Knowledge,Book,Utilization,KNOWLEDGE,BOOK,count</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -2005,7 +2047,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Chat,Analytics,Results,Knowledge,Utility,PageIndex</t>
+          <t>Chat,Analytics,Results,Knowledge,Utility,PageIndex,_render_ape_pageindex_tree,define_code</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -2035,6 +2077,7 @@
           <t>Chat タブのその他の機能</t>
         </is>
       </c>
+      <c r="D45" t="inlineStr"/>
       <c r="E45" t="inlineStr">
         <is>
           <t>Chat</t>
@@ -2069,12 +2112,12 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Chat の各ターン下部の「**Detail Information**」エクスパンダは3つのタブで構成:</t>
+          <t>Chat の各ターン下部の「**Detail Information**」エクスパンダは4つのタブで構成:</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Detail,Information,Chat,LLM,Input,System</t>
+          <t>Detail,Information,Chat,LLM,Input,System,dmu.count_token,get_detail_info</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2111,7 +2154,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Compare,Agent,Knowledge,Book,Analytics,Results</t>
+          <t>Compare,Agent,Knowledge,Book,Analytics,Results,Comment,SystemGuide</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2148,7 +2191,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>chat_input,Enter,Send,Discard</t>
+          <t>chat_input,Enter,Send,Discard,draft_input</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2180,12 +2223,12 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Chat 画面下部の `Batch Test (upload Q&amp;A xlsx)` エクスパンダから、Excel に並べた質問群を **現在のセッション＋現在のチャット設定** で 一括実行できます。Ground Truth が付いていれば、各回答を LLM＋決定的メトリクスで自動評価。**`Eval only` モード** では既存の Answer + Ground Truth 列だけを再スコアリング (LLM 呼び出しなし)。`Baseline` / `BaselineModel` 列は入力のまま保持され、Personal Evaluation の集約評価で使用されます。</t>
+          <t>Chat 画面下部の `Batch Test (upload Q&amp;A xlsx)` エクスパンダから、Excel に並べた質問群を **現在のセッション＋現在のチャット設定** で一括実行できます。Ground Truth が付いていれば、各回答を LLM＋決定的メトリクスで自動評価します。</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Batch,Test,Chat,Excel,Ground,Truth,Baseline,Eval,only</t>
+          <t>Batch,Test,Chat,Excel,Ground,Truth,Baseline,Eval</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2217,7 +2260,7 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>入力 Excel の列定義: `Question` (通常時 必須 / Eval only モードでは不要)、`Ground Truth` (評価トリガ)、`Answer` (実行結果が書き込まれる)、`Question Style` (クエリ前置)、`No` + `Memory No` (行ごとの履歴制御)、`Baseline` (ベンチマークモデルの回答、verbatim 保持)、`BaselineModel` (生成モデル名、verbatim 保持)。その他の列はそのまま出力に保持。`Memory No` セル値 `All` / `1,3` / 空 / 列なし で履歴の見え方を制御。</t>
+          <t>| 列 | 必須 | 説明 |</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
@@ -2254,7 +2297,7 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>出力 Excel は入力カラムを **元 xlsx の書式ごと** 維持しつつ以下を追加：`Persona` (multi-persona 時のみ)、`Answer` (エージェント応答)、`Verdict` (○/△/✕)、`Score` (0-100)、`Match` (Y/N 完全一致)、`Seq Ratio` / `Token F1` (決定的類似度)、`Eval` (LLM の 1 行コメント)。openpyxl オーバーレイで列幅・塗り・フォント・非対応シートは温存。行数が変わる時 (multi-persona 展開) のみ pandas 書き込みに fallback。</t>
+          <t>入力カラムを維持しつつ、以下を追加（既存なら上書き）:</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
@@ -2291,12 +2334,12 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>主要機能: (1) `Memory No` 列による粒度の高い履歴制御、(2) `Save Digest (BatchTest only)` トグルで digest 生成抑止、(3) **`Eval only` チェックボックス** — 既存の Answer + Ground Truth だけを `eval_answer_vs_groundtruth` で再評価 (Question 列は 評価コンテキストとして参照、なくても可)、(4) **`Baseline` / `BaselineModel` 列を verbatim 保持** (per-row の 追加評価はなし、Personal Evaluation で集約)、(5) **書式保持出力** (openpyxl overlay + fallback)、(6) サイドバーのペルソナ選択を反映した multi-persona 並列実行、(7) 進捗表示 (Eval only 時は `Re-evaluating Answer vs GT...`)。</t>
+          <t>- **行ごとの履歴制御は `Memory No` 列で完結**: 旧 `Memory Use (BatchTest only)` チェックボックスは廃止。チェックボックスより `No` + `Memory No` 列の組み合わせの方が「この質問は1行目と3行目だけ参照」「この質問は履歴なし」など粒度の高い制御ができる</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Memory,Use,BatchTest,Save,Digest,Eval,only,Baseline,format</t>
+          <t>Memory,Use,BatchTest,Save,Digest,Eval,only,Baseline</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2400,9 +2443,14 @@
           <t>内部実装メモ</t>
         </is>
       </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>- マルチペルソナ時のみ `MEMORY_SAVE=True` を自動セット（並列パスは `[STATUS]` チャンクしか stream しないため、各ペルソナ応答は chat_memory の sub_seq から読み出す）</t>
+        </is>
+      </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>MEMORY_SAVE,True,STATUS,LLM</t>
+          <t>MEMORY_SAVE,True,STATUS,LLM,dmt.eval_answer_vs_groundtruth,agent_53CompareTexts.json,dmt.critique_batch_results</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2434,7 +2482,7 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>サイドバーの **Evaluation** から、プラグイン式の評価テストを実行できる画面。`Allowed["Evaluation"]` 必須。バックエンドは `DigiM_Evaluation.py` (ローダー)。任意フック `default_agent()` で **専用エージェント固定** (再現性重視)、`list_categories()` で **カテゴリ絞り込み**、`llm_augment()` で **カテゴリごとの LLM 構造化分析を並列自動実行** できる。サイドバーの保存済セッションには **`Del` ボタン** (Chat と同じスタック配置)。</t>
+          <t>サイドバーの **Evaluation** から、プラグイン式の評価テストを実行できる画面です。`Allowed["Evaluation"]` 必須。バックエンドは [DigiM_Evaluation.py](DigiM_Evaluation.py) (ローダー)。</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
@@ -2471,12 +2519,12 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>`user/common/evaluation/&lt;評価名&gt;/main.py` に `Plugin` クラスを定義するだけで 自動検出。必須メソッド: `run(input_path)` / `render(result)` / `report_md(result)`。任意フック: `sample_path()` (テンプレート配信)、`default_agent()` (専用エージェント固定・再現性優先)、`list_categories()` (カテゴリ絞り込み UI)、`llm_augment(result, agent_file, service_info, user_info, categories=None) -&gt; dict` (Run analysis 時に自動発火、カテゴリごとの LLM 構造化分析を **並列** 実行し `{session_state_key: cache_entry}` を返す。エラーは `_llm_augment_errors` 特殊キーで surface)。</t>
+          <t>`user/common/evaluation/&lt;評価名&gt;/main.py` に `Plugin` クラスを定義するだけで自動検出。**プラグイン契約**:</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Plugin,default_agent,list_categories,llm_augment,parallel</t>
+          <t>Plugin,default_agent,list_categories,llm_augment,parallel,report_md,llm_evaluate</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2508,12 +2556,12 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>UI フロー: (1) プラグイン選択 → (2) 📎 Sample input: `&lt;filename&gt;` (**セキュリティ配慮でファイル名のみ表示**、Download template で byte-for-byte 配信・書式維持) → (3) Upload input (.xlsx) → (4) 🔒 Evaluation agent 固定表示 (プラグインの `default_agent()`) → (5) カテゴリチェックボックス → (6) **Run analysis** で解析＋**llm_augment 並列自動実行** → (7) **LLM Evaluation**: エージェント (別枠 selectbox) + **質問 (任意)** テキストエリア (空欄=定型講評 / 埋める=Q&amp;A モード) → (8) Generate Report + 自動保存 → (9) サイドバー保存履歴の各セッションに直下 **`Del` ボタン**。</t>
+          <t>1. **Evaluation プラグイン**ドロップダウン</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>UI,Evaluation,Download,Upload,Run,LLM,question,Q&amp;A,Del,agent</t>
+          <t>UI,Evaluation,Download,Upload,Run,LLM,question,Q&amp;A</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2545,12 +2593,12 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>人格評価7理論 (Big Five / Schwartz / SDT / Personal Strivings / Narrative Identity / Social Identity / Attachment) を一括スコアリング。Excel は 2 シート (Category メタ / PersonalTest Q&amp;A)。`Answer` (被評価 AI)、`Ground Truth` (対象者) に加え **`Baseline` 列** (ベンチマークモデル回答) を入れると、サマリータイル・レーダー・各カテゴリ スコア表に **A↔B / GT↔B の Cos/MAE/Diff** が追加表示 (人格形成・目標は対象外)。**人格形成は連続 0-1 採点** + 軸別 A/GT/比較 講評 (100-200 字)。**目標は 2×2 マトリクス (共通/共通しない × A/GT) + 手動再分類 (N:N ペア可) + 評点重み付き F1/Precision/Recall スコアリング**。**G3 決定論的パーサ** が LLM の edge 抜けを regex で補完 (`X と Y: シナジー` パターン)。編集は expander で折り畳み可、**変更を適用** ボタンで一括反映 → F1/P/R 自動再計算。**専用エージェント** `agent_66Evaluation.json` で構造化分析の再現性を担保。</t>
+          <t xml:space="preserve">人格評価7理論 (Big Five / Schwartz Value Theory / Self-Determination / Personal Strivings / Narrative Identity / Social Identity / Attachment) を一括スコアリング。テンプレートはプラグインフォルダ直下に同梱 (`user/common/evaluation/PersonalEvaluation/PersonalTestQA.xlsx`) — UI </t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>PersonalEvaluation,Big,Five,Schwartz,Baseline,F1,Precision,Recall,goals,N:N</t>
+          <t>PersonalEvaluation,Big,Five,Schwartz,Baseline,F1,Precision,Recall</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2582,7 +2630,7 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>`user/common/evaluation/&lt;新規名&gt;/main.py` に `Plugin` クラスを実装するだけで、サイドバーの Evaluation メニューに自動的にプラグインが現れる (再起動不要)。既存の PersonalEvaluation / AnimalFortune (動物占い) が実装参考。任意フック (`default_agent`, `list_categories`, `llm_augment`, `sample_path`) を追加すると UI が対応した振る舞いをする。</t>
+          <t>`user/common/evaluation/&lt;新規名&gt;/main.py` に `Plugin` クラスを実装するだけで、サイドバーの Evaluation メニューに自動的にプラグインが現れます (再起動不要)。既存の PersonalEvaluation / AnimalFortune (動物占い) が実装参考。</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
@@ -2654,9 +2702,14 @@
           <t>エンドポイント一覧</t>
         </is>
       </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>| メソッド | パス | 説明 |</t>
+        </is>
+      </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>POST,GET,CSV</t>
+          <t>POST,GET,CSV,attachments,attachment_urls,data,files,enabled</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2693,7 +2746,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>POST,run,HTTP,LLM,LOCKED,SERVICE_ID</t>
+          <t>POST,run,HTTP,LLM,LOCKED,SERVICE_ID,session_id,429</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2767,7 +2820,7 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>LINE,Messaging,API,Webhook,FastAPI,SERVICE_ID</t>
+          <t>LINE,Messaging,API,Webhook,FastAPI,SERVICE_ID,session_id</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2778,6 +2831,154 @@
       <c r="G65" t="inlineStr">
         <is>
           <t>15-4.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>DigiMPGシステムガイド</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>12-4</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>セッションサマリー（ユーザー定義のセッション状態文書）</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>**メモリダイジェストとは別**の、**ユーザーが書式を指定できるセッション状態文書**。対話のたびに軽量LLM (デフォルトは `agent_65SessionSummary.json` → Gemini-2.5-Flash) がバックグラウンドでテンプレートを埋めていき、次以降のプロンプトに `[Current Session Summary]` ブロックとして注入されます。</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>agent_65SessionSummary.json,status.yaml,Preset,DigiM_Util.save_yaml_file,_yaml_file_locks,SUPPORT_AGENT,agent_01DigitalMATSUMOTO.json,agent_10Sample.json</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>Chat タブのその他の機能</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>12-4.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>DigiMPGシステムガイド</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>14-5</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>プラグイン任意フック</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>`Plugin` に以下を追加すると WebUI が対応した振る舞いをします:</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>Plugin,_llm_augment_errors</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>Evaluation</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>14-5.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>DigiMPGシステムガイド</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>15-5</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>添付ファイル（attachments / attachment_urls / /run_multipart）</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>WebUI と同じ経路（`DigiMatsuExecute_Practice` の `in_contents=`）で LLM に文脈として添付ファイルを渡せます。3つの受け口があり、いずれも混在させて1リクエストで送れます。</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>DigiMatsuExecute_Practice,attachments,files,attachment_urls,DigiM_UrlFetch,passwd,attachments_processed,base64</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>API リファレンス</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>15-5.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>DigiMPGシステムガイド</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>15-6</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>セッションサマリー API</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>WebUI と同じ状態 (`status.yaml`) を API 経由で参照・変更できます。詳細な機能説明は [セッションサマリー](#セッションサマリーユーザー定義のセッション状態文書) を参照。</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>status.yaml,enabled,template,content,updated_at,Optional,session_summary_enabled,session_summary_template</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>API リファレンス</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>15-6.md</t>
         </is>
       </c>
     </row>

--- a/user/common/csv/pageindex/DigiMPGSystemGuide/DigiMPGSystemGuide.xlsx
+++ b/user/common/csv/pageindex/DigiMPGSystemGuide/DigiMPGSystemGuide.xlsx
@@ -438,7 +438,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G69"/>
+  <dimension ref="A1:G70"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2852,7 +2852,7 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>**メモリダイジェストとは別**の、**ユーザーが書式を指定できるセッション状態文書**。対話のたびに軽量LLM (デフォルトは `agent_65SessionSummary.json` → Gemini-2.5-Flash) がバックグラウンドでテンプレートを埋めていき、次以降のプロンプトに `[Current Session Summary]` ブロックとして注入されます。</t>
+          <t>**メモリダイジェストとは別**の、**ユーザーが書式を指定できるセッション状態文書**。対話のたびに軽量LLM (デフォルトは `agent_65SessionSummary.json` → Gemini-3.5-Flash) がバックグラウンドでテンプレートを埋めていき、次以降のプロンプトに `[Current Session Summary]` ブロックとして注入されます。</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
@@ -2979,6 +2979,43 @@
       <c r="G69" t="inlineStr">
         <is>
           <t>15-6.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>DigiMPGシステムガイド</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>12-5</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>Activate Sessions セレクタ（サイドバー）</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>過去に非表示にした（`Del` ボタンで `active=N` にした）セッションを再表示するための multiselect。**セッション名** で表示され、**最終更新日 (`last_update_date`) の降順**でソートされます（内部では ID を値として保持しているため、同名セッションでも一意に選べます）。Admin 以外は自分のセッションのみが対象。選択後に **`Activate`** ボタンで一括再表示。</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>Del,last_update_date,Activate</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>Chat タブのその他の機能</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>12-5.md</t>
         </is>
       </c>
     </row>

--- a/user/common/csv/pageindex/DigiMPGSystemGuide/DigiMPGSystemGuide.xlsx
+++ b/user/common/csv/pageindex/DigiMPGSystemGuide/DigiMPGSystemGuide.xlsx
@@ -438,7 +438,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G70"/>
+  <dimension ref="A1:G71"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -716,7 +716,6 @@
           <t>環境構築・インストレーション</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
           <t>環境構築・インストレーション</t>
@@ -1082,7 +1081,6 @@
           <t>セットアップガイド</t>
         </is>
       </c>
-      <c r="D18" t="inlineStr"/>
       <c r="E18" t="inlineStr">
         <is>
           <t>セットアップガイド</t>
@@ -1514,32 +1512,32 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8-12</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Knowledge Explorer</t>
+          <t>会話履歴の保存バックエンド</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Knowledge Explorerは、RAGデータの分析画面です。サイドバーのラジオボタン（Chat / Knowledge Explorer）から切り替えてアクセスします。</t>
+          <t>セッションのチャット履歴を JSON / PostgreSQL / CosmosDB のいずれかに保存できるバックエンド抽象化。setting.yaml の SESSION_STORE_METHOD で選択。</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Knowledge,Explorer,Chat,Allowed,Overall,Trend,users.json</t>
+          <t>SESSION_STORE_METHOD,PostgreSQL,CosmosDB,digim_chat_history,SessionStore,chat_memory</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Knowledge Explorer</t>
+          <t>セットアップガイド</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>9.md</t>
+          <t>8-12.md</t>
         </is>
       </c>
     </row>
@@ -1551,22 +1549,22 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>9-1</t>
+          <t>9</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>データソースの選択</t>
+          <t>Knowledge Explorer</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>ラジオボタンで **Collection（VectorDB）** / **Graph** / **PageIndex** を切り替えます。コレクション一覧は、選択中のエージェントの KNOWLEDGE および BOOK 設定に基づいてフィルタリングされます。PageIndex 選択時はツリー構造表示・ページ感度分析の専用画面になります。</t>
+          <t>Knowledge Explorerは、RAGデータの分析画面です。サイドバーのラジオボタン（Chat / Knowledge Explorer）から切り替えてアクセスします。</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Collection,VectorDB,PageIndex,KNOWLEDGE,BOOK,Persona,st.data_editor,save_graph_atomic</t>
+          <t>Knowledge,Explorer,Chat,Allowed,Overall,Trend,users.json</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1576,7 +1574,7 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>9-1.md</t>
+          <t>9.md</t>
         </is>
       </c>
     </row>
@@ -1588,22 +1586,22 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>9-2</t>
+          <t>9-1</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>1. Overall</t>
+          <t>データソースの選択</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>初期データ検索と散布図生成を統合したセクションです。</t>
+          <t>ラジオボタンで **Collection（VectorDB）** / **Graph** / **PageIndex** を切り替えます。コレクション一覧は、選択中のエージェントの KNOWLEDGE および BOOK 設定に基づいてフィルタリングされます。PageIndex 選択時はツリー構造表示・ページ感度分析の専用画面になります。</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Overall,PCA,SNE,Color,Marker,Dot</t>
+          <t>Collection,VectorDB,PageIndex,KNOWLEDGE,BOOK,Persona,st.data_editor,save_graph_atomic</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1613,7 +1611,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>9-2.md</t>
+          <t>9-1.md</t>
         </is>
       </c>
     </row>
@@ -1625,22 +1623,22 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>9-3</t>
+          <t>9-2</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>2. Trend（旧 時系列分析）</t>
+          <t>1. Overall</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>`create_date` が存在する場合に利用できます。**Total / 各RAG NAME** で固定表示します（View Mode 選択は廃止）。</t>
+          <t>初期データ検索と散布図生成を統合したセクションです。</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Trend,Total,NAME,View,Mode,RAG,create_date</t>
+          <t>Overall,PCA,SNE,Color,Marker,Dot</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1650,7 +1648,7 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>9-3.md</t>
+          <t>9-2.md</t>
         </is>
       </c>
     </row>
@@ -1662,22 +1660,22 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>9-4</t>
+          <t>9-3</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>3. Topic（旧 感度分析）</t>
+          <t>2. Trend（旧 時系列分析）</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>クエリテキストに対し、どの知識チャンクが強く反応するかを分析します（クラスタリングは含みません）。**Total / 各RAG NAME** で固定表示します。</t>
+          <t>`create_date` が存在する場合に利用できます。**Total / 各RAG NAME** で固定表示します（View Mode 選択は廃止）。</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Topic,Total,NAME,RAG,Collection,Overall</t>
+          <t>Trend,Total,NAME,View,Mode,RAG,create_date</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1687,7 +1685,7 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>9-4.md</t>
+          <t>9-3.md</t>
         </is>
       </c>
     </row>
@@ -1699,22 +1697,22 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>9-5</t>
+          <t>9-4</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>4. Ask Agent</t>
+          <t>3. Topic（旧 感度分析）</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>チャットと同じパイプライン（DigiMatsuExecute）を使用してエージェントに質問できます。Overall/Trend/Topic の表示中の解説が文脈として渡されます。</t>
+          <t>クエリテキストに対し、どの知識チャンクが強く反応するかを分析します（クラスタリングは含みません）。**Total / 各RAG NAME** で固定表示します。</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Ask,Agent,DigiMatsuExecute,Overall,Trend,Topic</t>
+          <t>Topic,Total,NAME,RAG,Collection,Overall</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1724,7 +1722,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>9-5.md</t>
+          <t>9-4.md</t>
         </is>
       </c>
     </row>
@@ -1736,22 +1734,22 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>9-6</t>
+          <t>9-5</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>PageIndex</t>
+          <t>4. Ask Agent</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>- **ツリー構造表示**: ページインデックスの階層をツリー形式で可視化</t>
+          <t>チャットと同じパイプライン（DigiMatsuExecute）を使用してエージェントに質問できます。Overall/Trend/Topic の表示中の解説が文脈として渡されます。</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>PageIndex</t>
+          <t>Ask,Agent,DigiMatsuExecute,Overall,Trend,Topic</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1761,7 +1759,7 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>9-6.md</t>
+          <t>9-5.md</t>
         </is>
       </c>
     </row>
@@ -1773,22 +1771,22 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>9-7</t>
+          <t>9-6</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>エクスポート・レポート</t>
+          <t>PageIndex</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>**Generate Report** ボタンで分析セッションを保存し、グラフ埋め込みの `.md` ファイルをダウンロードできます。各セクションの解説は、**ドロップダウンで表示中のバージョン**がそのまま出力されます。</t>
+          <t>- **ツリー構造表示**: ページインデックスの階層をツリー形式で可視化</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Generate,Report,.md</t>
+          <t>PageIndex</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1798,7 +1796,7 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>9-7.md</t>
+          <t>9-6.md</t>
         </is>
       </c>
     </row>
@@ -1810,22 +1808,22 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>9-8</t>
+          <t>9-7</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>セッション管理</t>
+          <t>エクスポート・レポート</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>| 項目 | 説明 |</t>
+          <t>**Generate Report** ボタンで分析セッションを保存し、グラフ埋め込みの `.md` ファイルをダウンロードできます。各セクションの解説は、**ドロップダウンで表示中のバージョン**がそのまま出力されます。</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>セッション管理</t>
+          <t>Generate,Report,.md</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1835,7 +1833,7 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>9-8.md</t>
+          <t>9-7.md</t>
         </is>
       </c>
     </row>
@@ -1847,32 +1845,32 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9-8</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>User Memory Explorer</t>
+          <t>セッション管理</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>ユーザーメモリ（Persona/Nowaday/History）を「ユーザー理解」の観点で分析する画面です。サイドバーのラジオボタン（Chat / Knowledge Explorer / **User Memory Explorer** / Scheduler）から切り替えます。バックエンドは `DigiM_UserMemoryExplorer.py`。</t>
+          <t>| 項目 | 説明 |</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>User,Memory,Explorer,Persona,Nowaday,History,DigiM_UserMemoryExplorer.py,users.json</t>
+          <t>セッション管理</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>User Memory Explorer</t>
+          <t>Knowledge Explorer</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>10.md</t>
+          <t>9-8.md</t>
         </is>
       </c>
     </row>
@@ -1884,32 +1882,32 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>10</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Agent Performance Explorer (APE)</t>
+          <t>User Memory Explorer</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>User Memory Explorer のエージェント版。サイドバーの **Agent Performance Explorer** から、特定エージェントの累積パフォーマンスを横断分析します。バックエンドは `DigiM_AgentPerformanceExplorer.py`。`Allowed["Agent Performance Explorer"]` が `true` のユーザーのみ利用可。</t>
+          <t>ユーザーメモリ（Persona/Nowaday/History）を「ユーザー理解」の観点で分析する画面です。サイドバーのラジオボタン（Chat / Knowledge Explorer / **User Memory Explorer** / Scheduler）から切り替えます。バックエンドは `DigiM_UserMemoryExplorer.py`。</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Agent,Performance,Explorer,APE,User,Memory,DigiM_AgentPerformanceExplorer.py</t>
+          <t>User,Memory,Explorer,Persona,Nowaday,History,DigiM_UserMemoryExplorer.py,users.json</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Agent Performance Explorer (APE)</t>
+          <t>User Memory Explorer</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>11.md</t>
+          <t>10.md</t>
         </is>
       </c>
     </row>
@@ -1921,22 +1919,22 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>11-1</t>
+          <t>11</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>データソース (PG → ライブ → アーカイブの優先順)</t>
+          <t>Agent Performance Explorer (APE)</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>| # | ソース | 用途 |</t>
+          <t>User Memory Explorer のエージェント版。サイドバーの **Agent Performance Explorer** から、特定エージェントの累積パフォーマンスを横断分析します。バックエンドは `DigiM_AgentPerformanceExplorer.py`。`Allowed["Agent Performance Explorer"]` が `true` のユーザーのみ利用可。</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>PG,PostgreSQL,Sessions,Export,DB,ZIP,ARCHIVE_DAYS</t>
+          <t>Agent,Performance,Explorer,APE,User,Memory,DigiM_AgentPerformanceExplorer.py</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1946,7 +1944,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>11-1.md</t>
+          <t>11.md</t>
         </is>
       </c>
     </row>
@@ -1958,22 +1956,22 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>11-2</t>
+          <t>11-1</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Tab 1: Overview</t>
+          <t>データソース (PG → ライブ → アーカイブの優先順)</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>- メトリック: Sessions / Turns / Users / Total chars / Avg turns/session</t>
+          <t>| # | ソース | 用途 |</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Tab,Overview,Sessions,Turns,Users,Total</t>
+          <t>PG,PostgreSQL,Sessions,Export,DB,ZIP,ARCHIVE_DAYS</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1983,7 +1981,7 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>11-2.md</t>
+          <t>11-1.md</t>
         </is>
       </c>
     </row>
@@ -1995,22 +1993,22 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>11-3</t>
+          <t>11-2</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Tab 2: Knowledge / Book Utilization</t>
+          <t>Tab 1: Overview</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>各 KNOWLEDGE / BOOK / PageIndex の **累積参照状況** を可視化:</t>
+          <t>- メトリック: Sessions / Turns / Users / Total chars / Avg turns/session</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Tab,Knowledge,Book,Utilization,KNOWLEDGE,BOOK,count</t>
+          <t>Tab,Overview,Sessions,Turns,Users,Total</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -2020,7 +2018,7 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>11-3.md</t>
+          <t>11-2.md</t>
         </is>
       </c>
     </row>
@@ -2032,22 +2030,22 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>11-4</t>
+          <t>11-3</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Chat の Analytics Results との連携</t>
+          <t>Tab 2: Knowledge / Book Utilization</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Chat タブの「**Analytics Results - Knowledge Utility**」ボタンも、引用RAGに **PageIndex が含まれていれば Page Tree** をその位置で描画 (参照ページを青、件数表示)。同じツリー描画ヘルパー `_render_ape_pageindex_tree` を共有しています。</t>
+          <t>各 KNOWLEDGE / BOOK / PageIndex の **累積参照状況** を可視化:</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Chat,Analytics,Results,Knowledge,Utility,PageIndex,_render_ape_pageindex_tree,define_code</t>
+          <t>Tab,Knowledge,Book,Utilization,KNOWLEDGE,BOOK,count</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -2057,7 +2055,7 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>11-4.md</t>
+          <t>11-3.md</t>
         </is>
       </c>
     </row>
@@ -2069,28 +2067,32 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11-4</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Chat タブのその他の機能</t>
-        </is>
-      </c>
-      <c r="D45" t="inlineStr"/>
+          <t>Chat の Analytics Results との連携</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>Chat タブの「**Analytics Results - Knowledge Utility**」ボタンも、引用RAGに **PageIndex が含まれていれば Page Tree** をその位置で描画 (参照ページを青、件数表示)。同じツリー描画ヘルパー `_render_ape_pageindex_tree` を共有しています。</t>
+        </is>
+      </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Chat</t>
+          <t>Chat,Analytics,Results,Knowledge,Utility,PageIndex,_render_ape_pageindex_tree,define_code</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Chat タブのその他の機能</t>
+          <t>Agent Performance Explorer (APE)</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>12.md</t>
+          <t>11-4.md</t>
         </is>
       </c>
     </row>
@@ -2102,22 +2104,17 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>12-1</t>
+          <t>12</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Detail Information タブ構成</t>
-        </is>
-      </c>
-      <c r="D46" t="inlineStr">
-        <is>
-          <t>Chat の各ターン下部の「**Detail Information**」エクスパンダは4つのタブで構成:</t>
+          <t>Chat タブのその他の機能</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Detail,Information,Chat,LLM,Input,System,dmu.count_token,get_detail_info</t>
+          <t>Chat</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2127,7 +2124,7 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>12-1.md</t>
+          <t>12.md</t>
         </is>
       </c>
     </row>
@@ -2139,22 +2136,22 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>12-2</t>
+          <t>12-1</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Compare Agent — Knowledge/Book 除外によるリグレッションテスト</t>
+          <t>Detail Information タブ構成</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>「Analytics Results - Compare Agents」で比較対象エージェントを選んだ後、`Exclude KNOWLEDGE (regression):` / `Exclude BOOK (regression):` のマルチセレクトで **特定の RAG_NAME を除外**して同一質問を再実行できます。</t>
+          <t>Chat の各ターン下部の「**Detail Information**」エクスパンダは4つのタブで構成:</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Compare,Agent,Knowledge,Book,Analytics,Results,Comment,SystemGuide</t>
+          <t>Detail,Information,Chat,LLM,Input,System,dmu.count_token,get_detail_info</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2164,7 +2161,7 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>12-2.md</t>
+          <t>12-1.md</t>
         </is>
       </c>
     </row>
@@ -2176,22 +2173,22 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>12-3</t>
+          <t>12-2</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>下書きモード (chat_input)</t>
+          <t>Compare Agent — Knowledge/Book 除外によるリグレッションテスト</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>直前のターンが実行中でも、メッセージ欄は **常に編集可能**。Enter 押下時に:</t>
+          <t>「Analytics Results - Compare Agents」で比較対象エージェントを選んだ後、`Exclude KNOWLEDGE (regression):` / `Exclude BOOK (regression):` のマルチセレクトで **特定の RAG_NAME を除外**して同一質問を再実行できます。</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>chat_input,Enter,Send,Discard,draft_input</t>
+          <t>Compare,Agent,Knowledge,Book,Analytics,Results,Comment,SystemGuide</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2201,7 +2198,7 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>12-3.md</t>
+          <t>12-2.md</t>
         </is>
       </c>
     </row>
@@ -2213,32 +2210,32 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>12-3</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Batch Test（一括 Q&amp;A 評価）</t>
+          <t>下書きモード (chat_input)</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Chat 画面下部の `Batch Test (upload Q&amp;A xlsx)` エクスパンダから、Excel に並べた質問群を **現在のセッション＋現在のチャット設定** で一括実行できます。Ground Truth が付いていれば、各回答を LLM＋決定的メトリクスで自動評価します。</t>
+          <t>直前のターンが実行中でも、メッセージ欄は **常に編集可能**。Enter 押下時に:</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Batch,Test,Chat,Excel,Ground,Truth,Baseline,Eval</t>
+          <t>chat_input,Enter,Send,Discard,draft_input</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Batch Test（一括 Q&amp;A 評価）</t>
+          <t>Chat タブのその他の機能</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>13.md</t>
+          <t>12-3.md</t>
         </is>
       </c>
     </row>
@@ -2250,22 +2247,22 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>13-1</t>
+          <t>13</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>入力 Excel フォーマット</t>
+          <t>Batch Test（一括 Q&amp;A 評価）</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>| 列 | 必須 | 説明 |</t>
+          <t>Chat 画面下部の `Batch Test (upload Q&amp;A xlsx)` エクスパンダから、Excel に並べた質問群を **現在のセッション＋現在のチャット設定** で一括実行できます。Ground Truth が付いていれば、各回答を LLM＋決定的メトリクスで自動評価します。</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Excel,Question,Style,Memory,Baseline,BaselineModel,Ground,Truth</t>
+          <t>Batch,Test,Chat,Excel,Ground,Truth,Baseline,Eval</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2275,7 +2272,7 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>13-1.md</t>
+          <t>13.md</t>
         </is>
       </c>
     </row>
@@ -2287,22 +2284,22 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>13-2</t>
+          <t>13-1</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>出力 Excel フォーマット</t>
+          <t>入力 Excel フォーマット</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>入力カラムを維持しつつ、以下を追加（既存なら上書き）:</t>
+          <t>| 列 | 必須 | 説明 |</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Excel,Persona,Answer,Verdict,LLM,Score,openpyxl,format</t>
+          <t>Excel,Question,Style,Memory,Baseline,BaselineModel,Ground,Truth</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2312,7 +2309,7 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>13-2.md</t>
+          <t>13-1.md</t>
         </is>
       </c>
     </row>
@@ -2324,22 +2321,22 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>13-3</t>
+          <t>13-2</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>主要機能</t>
+          <t>出力 Excel フォーマット</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>- **行ごとの履歴制御は `Memory No` 列で完結**: 旧 `Memory Use (BatchTest only)` チェックボックスは廃止。チェックボックスより `No` + `Memory No` 列の組み合わせの方が「この質問は1行目と3行目だけ参照」「この質問は履歴なし」など粒度の高い制御ができる</t>
+          <t>入力カラムを維持しつつ、以下を追加（既存なら上書き）:</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Memory,Use,BatchTest,Save,Digest,Eval,only,Baseline</t>
+          <t>Excel,Persona,Answer,Verdict,LLM,Score,openpyxl,format</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2349,7 +2346,7 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>13-3.md</t>
+          <t>13-2.md</t>
         </is>
       </c>
     </row>
@@ -2361,22 +2358,22 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>13-4</t>
+          <t>13-3</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Result Analysis（即表示）</t>
+          <t>主要機能</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>セッションフォルダの結果 xlsx を読み込み、シート横断サマリ＋シートごとの集計を表示:</t>
+          <t>- **行ごとの履歴制御は `Memory No` 列で完結**: 旧 `Memory Use (BatchTest only)` チェックボックスは廃止。チェックボックスより `No` + `Memory No` 列の組み合わせの方が「この質問は1行目と3行目だけ参照」「この質問は履歴なし」など粒度の高い制御ができる</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Result,Analysis,Verdict,Score,Exact,Match</t>
+          <t>Memory,Use,BatchTest,Save,Digest,Eval,only,Baseline</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2386,7 +2383,7 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>13-4.md</t>
+          <t>13-3.md</t>
         </is>
       </c>
     </row>
@@ -2398,22 +2395,22 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>13-5</t>
+          <t>13-4</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>LLM 評価（オンデマンド）</t>
+          <t>Result Analysis（即表示）</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>「LLM評価を生成」ボタンで、サマリ＋低スコア行（各シート 5 件まで）を LLM に渡し、以下を Markdown で生成。結果は `batch_results_&lt;TS&gt;.critique.md` に永続化:</t>
+          <t>セッションフォルダの結果 xlsx を読み込み、シート横断サマリ＋シートごとの集計を表示:</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>LLM,Markdown,TS,Agent,JSON,KNOWLEDGE</t>
+          <t>Result,Analysis,Verdict,Score,Exact,Match</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2423,7 +2420,7 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>13-5.md</t>
+          <t>13-4.md</t>
         </is>
       </c>
     </row>
@@ -2435,22 +2432,22 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>13-6</t>
+          <t>13-5</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>内部実装メモ</t>
+          <t>LLM 評価（オンデマンド）</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>- マルチペルソナ時のみ `MEMORY_SAVE=True` を自動セット（並列パスは `[STATUS]` チャンクしか stream しないため、各ペルソナ応答は chat_memory の sub_seq から読み出す）</t>
+          <t>「LLM評価を生成」ボタンで、サマリ＋低スコア行（各シート 5 件まで）を LLM に渡し、以下を Markdown で生成。結果は `batch_results_&lt;TS&gt;.critique.md` に永続化:</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>MEMORY_SAVE,True,STATUS,LLM,dmt.eval_answer_vs_groundtruth,agent_53CompareTexts.json,dmt.critique_batch_results</t>
+          <t>LLM,Markdown,TS,Agent,JSON,KNOWLEDGE</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2460,7 +2457,7 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>13-6.md</t>
+          <t>13-5.md</t>
         </is>
       </c>
     </row>
@@ -2472,32 +2469,32 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>13-6</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Evaluation</t>
+          <t>内部実装メモ</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>サイドバーの **Evaluation** から、プラグイン式の評価テストを実行できる画面です。`Allowed["Evaluation"]` 必須。バックエンドは [DigiM_Evaluation.py](DigiM_Evaluation.py) (ローダー)。</t>
+          <t>- マルチペルソナ時のみ `MEMORY_SAVE=True` を自動セット（並列パスは `[STATUS]` チャンクしか stream しないため、各ペルソナ応答は chat_memory の sub_seq から読み出す）</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Evaluation,Allowed,DigiM_Evaluation,default_agent,llm_augment,Del</t>
+          <t>MEMORY_SAVE,True,STATUS,LLM,dmt.eval_answer_vs_groundtruth,agent_53CompareTexts.json,dmt.critique_batch_results</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Evaluation</t>
+          <t>Batch Test（一括 Q&amp;A 評価）</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>14.md</t>
+          <t>13-6.md</t>
         </is>
       </c>
     </row>
@@ -2509,22 +2506,22 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>14-1</t>
+          <t>14</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>プラグインアーキテクチャ</t>
+          <t>Evaluation</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>`user/common/evaluation/&lt;評価名&gt;/main.py` に `Plugin` クラスを定義するだけで自動検出。**プラグイン契約**:</t>
+          <t>サイドバーの **Evaluation** から、プラグイン式の評価テストを実行できる画面です。`Allowed["Evaluation"]` 必須。バックエンドは [DigiM_Evaluation.py](DigiM_Evaluation.py) (ローダー)。</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Plugin,default_agent,list_categories,llm_augment,parallel,report_md,llm_evaluate</t>
+          <t>Evaluation,Allowed,DigiM_Evaluation,default_agent,llm_augment,Del</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2534,7 +2531,7 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>14-1.md</t>
+          <t>14.md</t>
         </is>
       </c>
     </row>
@@ -2546,22 +2543,22 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>14-2</t>
+          <t>14-1</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>UI フロー</t>
+          <t>プラグインアーキテクチャ</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>1. **Evaluation プラグイン**ドロップダウン</t>
+          <t>`user/common/evaluation/&lt;評価名&gt;/main.py` に `Plugin` クラスを定義するだけで自動検出。**プラグイン契約**:</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>UI,Evaluation,Download,Upload,Run,LLM,question,Q&amp;A</t>
+          <t>Plugin,default_agent,list_categories,llm_augment,parallel,report_md,llm_evaluate</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2571,7 +2568,7 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>14-2.md</t>
+          <t>14-1.md</t>
         </is>
       </c>
     </row>
@@ -2583,22 +2580,22 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>14-3</t>
+          <t>14-2</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>PersonalEvaluation プラグイン</t>
+          <t>UI フロー</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t xml:space="preserve">人格評価7理論 (Big Five / Schwartz Value Theory / Self-Determination / Personal Strivings / Narrative Identity / Social Identity / Attachment) を一括スコアリング。テンプレートはプラグインフォルダ直下に同梱 (`user/common/evaluation/PersonalEvaluation/PersonalTestQA.xlsx`) — UI </t>
+          <t>1. **Evaluation プラグイン**ドロップダウン</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>PersonalEvaluation,Big,Five,Schwartz,Baseline,F1,Precision,Recall</t>
+          <t>UI,Evaluation,Download,Upload,Run,LLM,question,Q&amp;A</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2608,7 +2605,7 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>14-3.md</t>
+          <t>14-2.md</t>
         </is>
       </c>
     </row>
@@ -2620,22 +2617,22 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>14-4</t>
+          <t>14-3</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>新評価の追加</t>
+          <t>PersonalEvaluation プラグイン</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>`user/common/evaluation/&lt;新規名&gt;/main.py` に `Plugin` クラスを実装するだけで、サイドバーの Evaluation メニューに自動的にプラグインが現れます (再起動不要)。既存の PersonalEvaluation / AnimalFortune (動物占い) が実装参考。</t>
+          <t xml:space="preserve">人格評価7理論 (Big Five / Schwartz Value Theory / Self-Determination / Personal Strivings / Narrative Identity / Social Identity / Attachment) を一括スコアリング。テンプレートはプラグインフォルダ直下に同梱 (`user/common/evaluation/PersonalEvaluation/PersonalTestQA.xlsx`) — UI </t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Plugin,Evaluation,PersonalEvaluation,AnimalFortune</t>
+          <t>PersonalEvaluation,Big,Five,Schwartz,Baseline,F1,Precision,Recall</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2645,7 +2642,7 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>14-4.md</t>
+          <t>14-3.md</t>
         </is>
       </c>
     </row>
@@ -2657,32 +2654,32 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14-4</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>API リファレンス</t>
+          <t>新評価の追加</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>FastAPI を起動すると、REST API 経由でエージェントを実行できます。LINE・Slack 等の外部サービスからの呼び出しにも対応しています。</t>
+          <t>`user/common/evaluation/&lt;新規名&gt;/main.py` に `Plugin` クラスを実装するだけで、サイドバーの Evaluation メニューに自動的にプラグインが現れます (再起動不要)。既存の PersonalEvaluation / AnimalFortune (動物占い) が実装参考。</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>API,FastAPI,REST,LINE,Slack</t>
+          <t>Plugin,Evaluation,PersonalEvaluation,AnimalFortune</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>API リファレンス</t>
+          <t>Evaluation</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>15.md</t>
+          <t>14-4.md</t>
         </is>
       </c>
     </row>
@@ -2694,22 +2691,22 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>15-1</t>
+          <t>15</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>エンドポイント一覧</t>
+          <t>API リファレンス</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>| メソッド | パス | 説明 |</t>
+          <t>FastAPI を起動すると、REST API 経由でエージェントを実行できます。LINE・Slack 等の外部サービスからの呼び出しにも対応しています。</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>POST,GET,CSV,attachments,attachment_urls,data,files,enabled</t>
+          <t>API,FastAPI,REST,LINE,Slack</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2719,7 +2716,7 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>15-1.md</t>
+          <t>15.md</t>
         </is>
       </c>
     </row>
@@ -2731,22 +2728,22 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>15-2</t>
+          <t>15-1</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>POST /run — メッセージ送信</t>
+          <t>エンドポイント一覧</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>1回の HTTP リクエストで LLM 実行が完結し、応答を直接返します。同一 `session_id` を指定すれば会話が継続されます。</t>
+          <t>| メソッド | パス | 説明 |</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>POST,run,HTTP,LLM,LOCKED,SERVICE_ID,session_id,429</t>
+          <t>POST,GET,CSV,attachments,attachment_urls,data,files,enabled</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2756,7 +2753,7 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>15-2.md</t>
+          <t>15-1.md</t>
         </is>
       </c>
     </row>
@@ -2768,22 +2765,22 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>15-3</t>
+          <t>15-2</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>実行例</t>
+          <t>POST /run — メッセージ送信</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>curl -s http://localhost:8899/health</t>
+          <t>1回の HTTP リクエストで LLM 実行が完結し、応答を直接返します。同一 `session_id` を指定すれば会話が継続されます。</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>POST,Content,Type,SERVICE_ID,API_TEST,SERVICE_DATA</t>
+          <t>POST,run,HTTP,LLM,LOCKED,SERVICE_ID,session_id,429</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2793,7 +2790,7 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>15-3.md</t>
+          <t>15-2.md</t>
         </is>
       </c>
     </row>
@@ -2805,22 +2802,22 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>15-4</t>
+          <t>15-3</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>LINE 連携での利用例</t>
+          <t>実行例</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>LINE Messaging API のWebhookからの呼び出しイメージです。</t>
+          <t>curl -s http://localhost:8899/health</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>LINE,Messaging,API,Webhook,FastAPI,SERVICE_ID,session_id</t>
+          <t>POST,Content,Type,SERVICE_ID,API_TEST,SERVICE_DATA</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2830,7 +2827,7 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>15-4.md</t>
+          <t>15-3.md</t>
         </is>
       </c>
     </row>
@@ -2842,32 +2839,32 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>12-4</t>
+          <t>15-4</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>セッションサマリー（ユーザー定義のセッション状態文書）</t>
+          <t>LINE 連携での利用例</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>**メモリダイジェストとは別**の、**ユーザーが書式を指定できるセッション状態文書**。対話のたびに軽量LLM (デフォルトは `agent_65SessionSummary.json` → Gemini-3.5-Flash) がバックグラウンドでテンプレートを埋めていき、次以降のプロンプトに `[Current Session Summary]` ブロックとして注入されます。</t>
+          <t>LINE Messaging API のWebhookからの呼び出しイメージです。</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>agent_65SessionSummary.json,status.yaml,Preset,DigiM_Util.save_yaml_file,_yaml_file_locks,SUPPORT_AGENT,agent_01DigitalMATSUMOTO.json,agent_10Sample.json</t>
+          <t>LINE,Messaging,API,Webhook,FastAPI,SERVICE_ID,session_id</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Chat タブのその他の機能</t>
+          <t>API リファレンス</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>12-4.md</t>
+          <t>15-4.md</t>
         </is>
       </c>
     </row>
@@ -2879,32 +2876,32 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>14-5</t>
+          <t>12-4</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>プラグイン任意フック</t>
+          <t>セッションサマリー（ユーザー定義のセッション状態文書）</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>`Plugin` に以下を追加すると WebUI が対応した振る舞いをします:</t>
+          <t>**メモリダイジェストとは別**の、**ユーザーが書式を指定できるセッション状態文書**。対話のたびに軽量LLM (デフォルトは `agent_65SessionSummary.json` → Gemini-3.5-Flash) がバックグラウンドでテンプレートを埋めていき、次以降のプロンプトに `[Current Session Summary]` ブロックとして注入されます。</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Plugin,_llm_augment_errors</t>
+          <t>agent_65SessionSummary.json,status.yaml,Preset,DigiM_Util.save_yaml_file,_yaml_file_locks,SUPPORT_AGENT,agent_01DigitalMATSUMOTO.json,agent_10Sample.json</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Evaluation</t>
+          <t>Chat タブのその他の機能</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>14-5.md</t>
+          <t>12-4.md</t>
         </is>
       </c>
     </row>
@@ -2916,32 +2913,32 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>15-5</t>
+          <t>14-5</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>添付ファイル（attachments / attachment_urls / /run_multipart）</t>
+          <t>プラグイン任意フック</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>WebUI と同じ経路（`DigiMatsuExecute_Practice` の `in_contents=`）で LLM に文脈として添付ファイルを渡せます。3つの受け口があり、いずれも混在させて1リクエストで送れます。</t>
+          <t>`Plugin` に以下を追加すると WebUI が対応した振る舞いをします:</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>DigiMatsuExecute_Practice,attachments,files,attachment_urls,DigiM_UrlFetch,passwd,attachments_processed,base64</t>
+          <t>Plugin,_llm_augment_errors</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>API リファレンス</t>
+          <t>Evaluation</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>15-5.md</t>
+          <t>14-5.md</t>
         </is>
       </c>
     </row>
@@ -2953,22 +2950,22 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>15-6</t>
+          <t>15-5</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>セッションサマリー API</t>
+          <t>添付ファイル（attachments / attachment_urls / /run_multipart）</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>WebUI と同じ状態 (`status.yaml`) を API 経由で参照・変更できます。詳細な機能説明は [セッションサマリー](#セッションサマリーユーザー定義のセッション状態文書) を参照。</t>
+          <t>WebUI と同じ経路（`DigiMatsuExecute_Practice` の `in_contents=`）で LLM に文脈として添付ファイルを渡せます。3つの受け口があり、いずれも混在させて1リクエストで送れます。</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>status.yaml,enabled,template,content,updated_at,Optional,session_summary_enabled,session_summary_template</t>
+          <t>DigiMatsuExecute_Practice,attachments,files,attachment_urls,DigiM_UrlFetch,passwd,attachments_processed,base64</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2978,7 +2975,7 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>15-6.md</t>
+          <t>15-5.md</t>
         </is>
       </c>
     </row>
@@ -2990,30 +2987,67 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
+          <t>15-6</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>セッションサマリー API</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>WebUI と同じ状態 (`status.yaml`) を API 経由で参照・変更できます。詳細な機能説明は [セッションサマリー](#セッションサマリーユーザー定義のセッション状態文書) を参照。</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>status.yaml,enabled,template,content,updated_at,Optional,session_summary_enabled,session_summary_template</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>API リファレンス</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>15-6.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>DigiMPGシステムガイド</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
           <t>12-5</t>
         </is>
       </c>
-      <c r="C70" t="inlineStr">
+      <c r="C71" t="inlineStr">
         <is>
           <t>Activate Sessions セレクタ（サイドバー）</t>
         </is>
       </c>
-      <c r="D70" t="inlineStr">
+      <c r="D71" t="inlineStr">
         <is>
           <t>過去に非表示にした（`Del` ボタンで `active=N` にした）セッションを再表示するための multiselect。**セッション名** で表示され、**最終更新日 (`last_update_date`) の降順**でソートされます（内部では ID を値として保持しているため、同名セッションでも一意に選べます）。Admin 以外は自分のセッションのみが対象。選択後に **`Activate`** ボタンで一括再表示。</t>
         </is>
       </c>
-      <c r="E70" t="inlineStr">
+      <c r="E71" t="inlineStr">
         <is>
           <t>Del,last_update_date,Activate</t>
         </is>
       </c>
-      <c r="F70" t="inlineStr">
+      <c r="F71" t="inlineStr">
         <is>
           <t>Chat タブのその他の機能</t>
         </is>
       </c>
-      <c r="G70" t="inlineStr">
+      <c r="G71" t="inlineStr">
         <is>
           <t>12-5.md</t>
         </is>
